--- a/check.xlsx
+++ b/check.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>qq</t>
   </si>
@@ -35,25 +35,61 @@
     <t>name</t>
   </si>
   <si>
-    <t>qjw</t>
-  </si>
-  <si>
-    <t>cl</t>
-  </si>
-  <si>
-    <t>sty</t>
-  </si>
-  <si>
-    <t>xft</t>
-  </si>
-  <si>
-    <t>xkj</t>
-  </si>
-  <si>
-    <t>cyh</t>
-  </si>
-  <si>
-    <t>stl</t>
+    <t>钱嘉炜</t>
+  </si>
+  <si>
+    <t>hellocccl</t>
+  </si>
+  <si>
+    <t>肖方涛</t>
+  </si>
+  <si>
+    <t>TGSTY</t>
+  </si>
+  <si>
+    <t>Ryanzi</t>
+  </si>
+  <si>
+    <t>Jokerlove</t>
+  </si>
+  <si>
+    <t>徐凯杰</t>
+  </si>
+  <si>
+    <t>陈宇昊</t>
+  </si>
+  <si>
+    <t>Icyecho</t>
+  </si>
+  <si>
+    <t>karashi_</t>
+  </si>
+  <si>
+    <t>朱楠</t>
+  </si>
+  <si>
+    <t>佘相东</t>
+  </si>
+  <si>
+    <t>徐锐</t>
+  </si>
+  <si>
+    <t>应汶妤</t>
+  </si>
+  <si>
+    <t>程江峰</t>
+  </si>
+  <si>
+    <t>诸葛邵旭</t>
+  </si>
+  <si>
+    <t>倪倩文</t>
+  </si>
+  <si>
+    <t>郑扬</t>
+  </si>
+  <si>
+    <t>周益行</t>
   </si>
 </sst>
 </file>
@@ -82,8 +118,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -696,13 +732,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1049,83 +1090,179 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="11.5"/>
+    <col min="1" max="1" width="11.5" style="1"/>
+    <col min="2" max="2" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>1040530821</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>852227286</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4">
+      <c r="A4" s="1">
+        <v>1533585158</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1">
         <v>2810640380</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>1533585158</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
+        <v>982563202</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1">
+        <v>1541593711</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1">
         <v>1109238402</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="3">
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1">
         <v>2832640093</v>
       </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1">
+        <v>1137157342</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1">
         <v>2286475331</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="2">
-        <v>1137157342</v>
-      </c>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1">
+        <v>2870365142</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1">
+        <v>1077282002</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1">
+        <v>1831944862</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="3">
+        <v>1075057793</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1">
+        <v>3057155010</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1">
+        <v>2075958609</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1">
+        <v>3200262498</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1">
+        <v>2171682519</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1">
+        <v>875722864</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>